--- a/Bin/A-QIP-WS001-01D.xlsx
+++ b/Bin/A-QIP-WS001-01D.xlsx
@@ -1,31 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP SOURCE CODE QC 20251101\Bin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP SOURCE CODE\Bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5392ED9F-9B9A-409C-9209-754D21249C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vật tư + phụ liệu" sheetId="11" r:id="rId1"/>
   </sheets>
   <calcPr calcId="145621"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -610,7 +600,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
@@ -893,7 +883,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -922,6 +912,21 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -944,41 +949,29 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
-    <cellStyle name="Comma 2" xfId="4"/>
-    <cellStyle name="Comma 4 2" xfId="5"/>
-    <cellStyle name="Excel Built-in Normal" xfId="6"/>
+    <cellStyle name="Comma 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Comma 4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3"/>
-    <cellStyle name="Normal 2 2" xfId="7"/>
-    <cellStyle name="Normal 2 3" xfId="8"/>
-    <cellStyle name="Normal 3" xfId="9"/>
-    <cellStyle name="Normal 4" xfId="10"/>
-    <cellStyle name="Normal 5" xfId="11"/>
-    <cellStyle name="Normal 6" xfId="12"/>
-    <cellStyle name="Normal 6 2" xfId="13"/>
-    <cellStyle name="Normal 7" xfId="14"/>
-    <cellStyle name="Normal 8" xfId="15"/>
-    <cellStyle name="Normal 9" xfId="16"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2 3" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 4" xfId="10" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 5" xfId="11" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 6" xfId="12" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 6 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 7" xfId="14" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 8" xfId="15" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 9" xfId="16" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
-    <cellStyle name="Percent 4 2" xfId="17"/>
-    <cellStyle name="Style 1" xfId="18"/>
-    <cellStyle name="一般_Sheet1" xfId="2"/>
+    <cellStyle name="Percent 4 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Style 1" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="一般_Sheet1" xfId="2" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -994,9 +987,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1034,9 +1027,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1071,7 +1064,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1106,7 +1099,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1279,8 +1272,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="51.140625" style="7" customWidth="1"/>
@@ -1300,89 +1293,89 @@
     <col min="15" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="20" customFormat="1" ht="82.5" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:14" s="10" customFormat="1" ht="82.5" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
-    <row r="2" spans="1:14" s="21" customFormat="1" ht="42" customHeight="1">
+    <row r="2" spans="1:14" s="11" customFormat="1" ht="42" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="14" t="s">
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15" t="s">
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
     </row>
-    <row r="3" spans="1:14" s="21" customFormat="1" ht="47.25" customHeight="1">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:14" s="11" customFormat="1" ht="47.25" customHeight="1">
+      <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="16" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
     </row>
     <row r="4" spans="1:14" ht="90" customHeight="1">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
       <c r="G4" s="8" t="s">
         <v>8</v>
       </c>
@@ -1425,119 +1418,195 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" ht="42" customHeight="1">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="18" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18" t="s">
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A7:C11"/>
-    <mergeCell ref="D7:F11"/>
-    <mergeCell ref="G7:J11"/>
-    <mergeCell ref="K7:N11"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="A7:B14"/>
+    <mergeCell ref="C7:E14"/>
+    <mergeCell ref="F7:J14"/>
+    <mergeCell ref="K7:N14"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -1551,6 +1620,10 @@
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:H2"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0.196850393700787" header="0.196850393700787" footer="0.1"/>
